--- a/Havineni_RSS_Feed.xlsx
+++ b/Havineni_RSS_Feed.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Categroy name</t>
   </si>
@@ -367,13 +367,33 @@
   </si>
   <si>
     <t>https://lomdotchasidut.libsyn.com/podcast/category/%D7%AA%D7%9C%D7%9E%D7%95%D7%93+%D7%99%D7%A8%D7%95%D7%A9%D7%9C%D7%9E%D7%99</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>ספר חפץ חיים</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://lomdotchasidut.libsyn.com/podcast/category/%D7%A1%D7%A4%D7%A8+%D7%97%D7%A4%D7%A5+%D7%97%D7%99%D7%99%D7%9D</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -399,6 +419,16 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -420,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -435,6 +465,12 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -896,6 +932,14 @@
         <v>59</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="A2"/>
@@ -956,7 +1000,9 @@
     <hyperlink r:id="rId56" ref="B29"/>
     <hyperlink r:id="rId57" ref="A30"/>
     <hyperlink r:id="rId58" ref="B30"/>
+    <hyperlink r:id="rId59" ref="A31"/>
+    <hyperlink r:id="rId60" ref="B31"/>
   </hyperlinks>
-  <drawing r:id="rId59"/>
+  <drawing r:id="rId61"/>
 </worksheet>
 </file>